--- a/artfynd/A 27708-2024 artfynd.xlsx
+++ b/artfynd/A 27708-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,27 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118608293</v>
+        <v>137342625</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,24 +823,20 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kärren, Kärren, Sm</t>
+          <t>Kärren, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579256</v>
+        <v>579175</v>
       </c>
       <c r="R3" t="n">
-        <v>6398133</v>
+        <v>6398194</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,24 +890,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118608293</t>
+          <t>https://artportalen.se/Sighting/137342625</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118611275</v>
+        <v>118608293</v>
       </c>
       <c r="B4" t="n">
         <v>57950</v>
@@ -940,19 +936,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kammartorp, Kammartorp, Sm</t>
+          <t>Kärren, Kärren, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579275</v>
+        <v>579256</v>
       </c>
       <c r="R4" t="n">
-        <v>6398015</v>
+        <v>6398133</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,6 +1017,118 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118608293</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118611275</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kammartorp, Kammartorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>579275</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6398015</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118611275</t>
         </is>
@@ -1026,6 +1139,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27708-2024 artfynd.xlsx
+++ b/artfynd/A 27708-2024 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137342625</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27708-2024 artfynd.xlsx
+++ b/artfynd/A 27708-2024 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137342625</v>
       </c>
       <c r="B3" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27708-2024 artfynd.xlsx
+++ b/artfynd/A 27708-2024 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137342625</v>
       </c>
       <c r="B3" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
